--- a/lesson3/answer2.xlsx
+++ b/lesson3/answer2.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5202535317041.715</v>
+        <v>5202535317041.714</v>
       </c>
     </row>
     <row r="6">
